--- a/생활속의 경제/생활속의 경제_에너지경제.xlsx
+++ b/생활속의 경제/생활속의 경제_에너지경제.xlsx
@@ -5,15 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Teaching\생활속의 경제\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D2B5FE-E53F-40FA-A270-FD66F63CA44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97056FE2-B1E9-441E-9165-756391956CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57495" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{F54B2F44-06BE-4BFE-8C64-D9E3AB5170D4}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{F54B2F44-06BE-4BFE-8C64-D9E3AB5170D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
   <si>
     <t>총비용</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -122,11 +124,129 @@
     <t>통행료</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>탄소배출량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>휘발유소비량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MJ/liter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>휘발유발열량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배출계수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tC/MJ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MWh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MJ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kWh/km</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KTX전력소비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kWh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전력 탄소배출계수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tips.energy.or.kr/carbon/Ggas_tatistics03.do</t>
+  </si>
+  <si>
+    <t>tCO2eq./MWh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tC/MWh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버스 탄소배출양</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김형철, '충남 CNG버스 보급에 따른 경제적 효과 검토', 2017.12.18. 현안과제연구 Issue Report</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에너지소비량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발열량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kgC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1인당 탄소배출량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버스승객</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tC/인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kgC/인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="0.00000"/>
+    <numFmt numFmtId="177" formatCode="0.0000"/>
+    <numFmt numFmtId="178" formatCode="0.000"/>
+    <numFmt numFmtId="179" formatCode="0.0"/>
+    <numFmt numFmtId="188" formatCode="0.000000_);[Red]\(0.000000\)"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -181,17 +301,29 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -209,6 +341,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>219074</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>392980</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EA5B553-B009-4A1D-3886-FD8DB261A392}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3943350" y="438149"/>
+          <a:ext cx="8279680" cy="2581275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -528,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED93658-B13C-4E78-AF4A-E8F744334A5D}">
-  <dimension ref="A2:I40"/>
+  <dimension ref="A2:I48"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
@@ -547,14 +728,11 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="D5" s="2"/>
-    </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>4</v>
       </c>
       <c r="D6" t="s">
@@ -595,7 +773,7 @@
         <v>1500000</v>
       </c>
       <c r="F8" s="1">
-        <f>C8/((1+$B$2)^A8)</f>
+        <f t="shared" ref="F8:F22" si="1">C8/((1+$B$2)^A8)</f>
         <v>1428571.4285714284</v>
       </c>
       <c r="H8">
@@ -617,7 +795,7 @@
         <v>1500000</v>
       </c>
       <c r="F9" s="1">
-        <f>C9/((1+$B$2)^A9)</f>
+        <f t="shared" si="1"/>
         <v>1360544.2176870748</v>
       </c>
       <c r="H9">
@@ -639,7 +817,7 @@
         <v>1500000</v>
       </c>
       <c r="F10" s="1">
-        <f>C10/((1+$B$2)^A10)</f>
+        <f t="shared" si="1"/>
         <v>1295756.3977972139</v>
       </c>
       <c r="H10">
@@ -661,7 +839,7 @@
         <v>1500000</v>
       </c>
       <c r="F11" s="1">
-        <f>C11/((1+$B$2)^A11)</f>
+        <f t="shared" si="1"/>
         <v>1234053.7121878229</v>
       </c>
       <c r="H11">
@@ -683,7 +861,7 @@
         <v>1500000</v>
       </c>
       <c r="F12" s="1">
-        <f>C12/((1+$B$2)^A12)</f>
+        <f t="shared" si="1"/>
         <v>1175289.2497026885</v>
       </c>
       <c r="H12">
@@ -705,7 +883,7 @@
         <v>1500000</v>
       </c>
       <c r="F13" s="1">
-        <f>C13/((1+$B$2)^A13)</f>
+        <f t="shared" si="1"/>
         <v>1119323.0949549414</v>
       </c>
       <c r="H13">
@@ -727,7 +905,7 @@
         <v>1500000</v>
       </c>
       <c r="F14" s="1">
-        <f>C14/((1+$B$2)^A14)</f>
+        <f t="shared" si="1"/>
         <v>1066021.9951951823</v>
       </c>
       <c r="H14">
@@ -749,7 +927,7 @@
         <v>1500000</v>
       </c>
       <c r="F15" s="1">
-        <f>C15/((1+$B$2)^A15)</f>
+        <f t="shared" si="1"/>
         <v>1015259.0430430308</v>
       </c>
       <c r="H15">
@@ -771,7 +949,7 @@
         <v>1500000</v>
       </c>
       <c r="F16" s="1">
-        <f>C16/((1+$B$2)^A16)</f>
+        <f t="shared" si="1"/>
         <v>966913.37432669592</v>
       </c>
       <c r="H16">
@@ -793,7 +971,7 @@
         <v>1500000</v>
       </c>
       <c r="F17" s="1">
-        <f>C17/((1+$B$2)^A17)</f>
+        <f t="shared" si="1"/>
         <v>920869.88031113893</v>
       </c>
       <c r="H17">
@@ -815,7 +993,7 @@
         <v>1500000</v>
       </c>
       <c r="F18" s="1">
-        <f>C18/((1+$B$2)^A18)</f>
+        <f t="shared" si="1"/>
         <v>877018.93362965609</v>
       </c>
       <c r="H18">
@@ -837,7 +1015,7 @@
         <v>1500000</v>
       </c>
       <c r="F19" s="1">
-        <f>C19/((1+$B$2)^A19)</f>
+        <f t="shared" si="1"/>
         <v>835256.12726633926</v>
       </c>
       <c r="H19">
@@ -859,7 +1037,7 @@
         <v>1500000</v>
       </c>
       <c r="F20" s="1">
-        <f>C20/((1+$B$2)^A20)</f>
+        <f t="shared" si="1"/>
         <v>795482.02596794197</v>
       </c>
       <c r="H20">
@@ -881,7 +1059,7 @@
         <v>1500000</v>
       </c>
       <c r="F21" s="1">
-        <f>C21/((1+$B$2)^A21)</f>
+        <f t="shared" si="1"/>
         <v>757601.92949327826</v>
       </c>
       <c r="H21">
@@ -903,7 +1081,7 @@
         <v>1500000</v>
       </c>
       <c r="F22" s="1">
-        <f>C22/((1+$B$2)^A22)</f>
+        <f t="shared" si="1"/>
         <v>721525.64713645529</v>
       </c>
       <c r="H22">
@@ -944,12 +1122,12 @@
       <c r="G29" t="s">
         <v>12</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="2">
         <f>H27*H28</f>
         <v>51207.708107844148</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>7</v>
       </c>
@@ -960,7 +1138,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>8</v>
       </c>
@@ -971,7 +1149,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>5</v>
       </c>
@@ -982,7 +1160,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>13</v>
       </c>
@@ -991,7 +1169,7 @@
         <v>33833.866666666661</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>14</v>
       </c>
@@ -999,17 +1177,318 @@
         <v>15300</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
         <v>0</v>
       </c>
       <c r="C40" s="1">
         <f>SUM(H29,C37,C38)</f>
         <v>100341.57477451081</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="D45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46">
+        <v>32.4</v>
+      </c>
+      <c r="D46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47">
+        <v>1.9730999999999999E-2</v>
+      </c>
+      <c r="D47" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C48">
+        <f>C45*C46*C47</f>
+        <v>12.082475159999998</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CEC1E91-8344-47F1-8923-68E668F59321}">
+  <dimension ref="B1:I15"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.08203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.4173</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5">
+        <v>3600</v>
+      </c>
+      <c r="H5" s="5">
+        <f>H4*(12/44)</f>
+        <v>0.1138090909090909</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="H6" s="7">
+        <f>H5/C5</f>
+        <v>3.1613636363636364E-5</v>
+      </c>
+      <c r="I6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>23.74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="C10">
+        <v>258</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="C11" s="1">
+        <f>C9*C10</f>
+        <v>6124.9199999999992</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="C12" s="1">
+        <f>C11/1000</f>
+        <v>6.1249199999999995</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="C13">
+        <f>C12*C5</f>
+        <v>22049.712</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="C14">
+        <v>0.114</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="C15">
+        <f>C13*C14</f>
+        <v>2513.6671679999999</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37A68708-5D2A-49EA-B5AD-AA7529CE9936}">
+  <dimension ref="A2:G18"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.58203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="6">
+        <f>B4/B5</f>
+        <v>6.8273092369477908</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>2.0089999999999999E-5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="4">
+        <f>B7*B8*B9</f>
+        <v>5.1846722891566261E-3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B12" s="6">
+        <f>B11*1000</f>
+        <v>5.1846722891566257</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3">
+        <f>B11/B14</f>
+        <v>5.1846722891566257E-4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B18" s="3">
+        <f>B12/B14</f>
+        <v>0.51846722891566255</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>